--- a/data/trans_camb/IP22_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 18,66</t>
+          <t>-1,3; 17,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 14,32</t>
+          <t>-5,28; 13,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 12,84</t>
+          <t>-4,57; 13,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 12,1</t>
+          <t>-8,42; 13,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 6,04</t>
+          <t>-12,66; 6,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 0,68</t>
+          <t>-16,48; 1,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 11,77</t>
+          <t>-1,88; 12,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 6,79</t>
+          <t>-5,94; 6,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,64</t>
+          <t>-8,2; 4,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 160,49</t>
+          <t>-6,77; 153,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 121,89</t>
+          <t>-25,58; 111,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 106,92</t>
+          <t>-23,46; 115,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 65,97</t>
+          <t>-31,6; 70,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,77; 32,04</t>
+          <t>-46,59; 34,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 4,67</t>
+          <t>-59,64; 7,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 73,53</t>
+          <t>-8,95; 76,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 45,85</t>
+          <t>-27,8; 43,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 30,7</t>
+          <t>-37,17; 26,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 10,04</t>
+          <t>-11,21; 9,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 0,58</t>
+          <t>-17,38; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,33; -4,93</t>
+          <t>-22,15; -3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 14,7</t>
+          <t>-6,65; 14,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 1,25</t>
+          <t>-17,85; 1,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 0,06</t>
+          <t>-19,17; 0,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 10,41</t>
+          <t>-5,41; 9,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -1,87</t>
+          <t>-14,89; -1,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -4,29</t>
+          <t>-18,17; -5,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 53,23</t>
+          <t>-36,43; 49,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,28; 4,04</t>
+          <t>-56,94; 9,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,56; -21,05</t>
+          <t>-72,89; -16,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 79,48</t>
+          <t>-23,38; 83,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 7,6</t>
+          <t>-59,58; 6,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,65; 6,08</t>
+          <t>-66,23; 5,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 51,45</t>
+          <t>-18,84; 47,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,83; -8,66</t>
+          <t>-51,86; -7,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,15; -18,52</t>
+          <t>-64,57; -23,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 8,35</t>
+          <t>-14,35; 8,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 0,64</t>
+          <t>-20,25; 1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 4,03</t>
+          <t>-20,69; 2,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 9,35</t>
+          <t>-10,27; 9,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 5,08</t>
+          <t>-14,57; 5,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 11,0</t>
+          <t>-12,18; 10,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 5,88</t>
+          <t>-9,64; 5,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 1,0</t>
+          <t>-15,27; 0,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 4,34</t>
+          <t>-13,21; 3,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 53,75</t>
+          <t>-47,8; 53,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 5,39</t>
+          <t>-70,61; 9,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,26; 24,49</t>
+          <t>-68,49; 15,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 50,72</t>
+          <t>-37,08; 50,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 28,41</t>
+          <t>-53,52; 28,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,06; 60,65</t>
+          <t>-45,2; 57,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 29,81</t>
+          <t>-35,2; 25,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,26; 5,24</t>
+          <t>-54,82; 2,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 21,48</t>
+          <t>-48,93; 18,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,81</t>
+          <t>0,74; 14,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 4,92</t>
+          <t>-7,34; 4,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 4,56</t>
+          <t>-11,99; 5,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 13,89</t>
+          <t>-0,39; 13,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 0,44</t>
+          <t>-12,64; 0,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 1,01</t>
+          <t>-13,03; 1,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,53</t>
+          <t>2,2; 12,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 0,93</t>
+          <t>-7,81; 0,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 0,7</t>
+          <t>-10,28; 1,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 76,09</t>
+          <t>3,59; 83,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 27,9</t>
+          <t>-31,25; 26,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 26,57</t>
+          <t>-50,58; 30,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 73,63</t>
+          <t>-2,13; 69,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 1,93</t>
+          <t>-49,27; 3,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 6,16</t>
+          <t>-50,08; 6,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,84; 64,34</t>
+          <t>8,66; 61,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 4,8</t>
+          <t>-33,01; 3,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 3,72</t>
+          <t>-42,73; 7,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 13,27</t>
+          <t>-1,96; 13,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 12,08</t>
+          <t>-3,71; 12,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 8,75</t>
+          <t>-7,67; 8,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 18,5</t>
+          <t>1,66; 19,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 5,66</t>
+          <t>-9,95; 5,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 2,54</t>
+          <t>-12,92; 2,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 13,45</t>
+          <t>1,71; 13,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 6,07</t>
+          <t>-5,42; 5,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 2,85</t>
+          <t>-8,09; 2,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 126,35</t>
+          <t>-12,09; 126,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 118,97</t>
+          <t>-20,96; 116,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 77,28</t>
+          <t>-39,72; 74,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,19; 111,26</t>
+          <t>5,83; 114,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 35,95</t>
+          <t>-41,57; 32,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 16,64</t>
+          <t>-55,84; 19,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,63; 86,17</t>
+          <t>7,15; 85,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 41,68</t>
+          <t>-26,82; 37,02</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,18; 19,88</t>
+          <t>-39,77; 17,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 5,54</t>
+          <t>-18,85; 3,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -0,38</t>
+          <t>-20,47; 0,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,91; -0,38</t>
+          <t>-22,23; -2,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 16,66</t>
+          <t>-4,74; 16,39</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 6,77</t>
+          <t>-13,17; 5,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -0,01</t>
+          <t>-17,94; -0,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 7,24</t>
+          <t>-7,46; 7,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 0,14</t>
+          <t>-14,42; -0,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,27; -4,26</t>
+          <t>-17,39; -4,17</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-72,42; 41,72</t>
+          <t>-72,2; 24,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,44; 1,91</t>
+          <t>-76,58; 10,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,09; -0,56</t>
+          <t>-83,04; -2,86</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 130,18</t>
+          <t>-22,32; 132,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 60,24</t>
+          <t>-60,4; 45,32</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 10,14</t>
+          <t>-79,53; 5,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 47,48</t>
+          <t>-33,76; 48,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 2,56</t>
+          <t>-63,74; -1,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-75,93; -24,8</t>
+          <t>-76,59; -24,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,3</t>
+          <t>-0,45; 7,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 1,23</t>
+          <t>-5,78; 1,03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -0,38</t>
+          <t>-8,04; -0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,09</t>
+          <t>1,24; 9,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,45; -1,42</t>
+          <t>-8,35; -1,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -3,21</t>
+          <t>-10,22; -3,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,26</t>
+          <t>2,09; 7,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -1,19</t>
+          <t>-6,21; -1,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -2,81</t>
+          <t>-8,11; -2,92</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 39,46</t>
+          <t>-2,61; 38,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 6,98</t>
+          <t>-26,13; 5,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,72; -1,67</t>
+          <t>-37,22; 1,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,57; 45,93</t>
+          <t>4,89; 43,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-34,98; -6,71</t>
+          <t>-35,4; -6,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,82; -15,25</t>
+          <t>-43,57; -15,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,82; 36,87</t>
+          <t>8,78; 36,18</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-27,61; -5,82</t>
+          <t>-27,69; -6,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-36,2; -13,97</t>
+          <t>-37,03; -14,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP22_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-7,48</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,98</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,29</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,45</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,46</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 17,58</t>
+          <t>-8,74; 11,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 13,13</t>
+          <t>-13,02; 6,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 13,4</t>
+          <t>-16,32; 0,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 13,11</t>
+          <t>-0,7; 18,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 6,18</t>
+          <t>-4,9; 13,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 1,03</t>
+          <t>-3,13; 14,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 12,06</t>
+          <t>-1,38; 13,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 6,65</t>
+          <t>-5,56; 7,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 4,19</t>
+          <t>-7,4; 4,82</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-14,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-33,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>54,44%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>25,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30,03%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-14,7%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,28%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,52%</t>
+          <t>-7,71%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 153,87</t>
+          <t>-30,74; 64,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 111,34</t>
+          <t>-48,75; 35,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 115,77</t>
+          <t>-59,96; 3,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 70,62</t>
+          <t>-5,44; 155,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 34,31</t>
+          <t>-25,86; 116,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,64; 7,29</t>
+          <t>-16,38; 117,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 76,89</t>
+          <t>-6,41; 80,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 43,97</t>
+          <t>-25,82; 47,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 26,02</t>
+          <t>-33,89; 30,95</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-8,37</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-9,54</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-7,87</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-8,37</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,5</t>
+          <t>-13,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,55</t>
+          <t>-11,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 9,66</t>
+          <t>-6,13; 14,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 1,87</t>
+          <t>-17,47; 1,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,15; -3,57</t>
+          <t>-18,9; -0,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 14,85</t>
+          <t>-9,81; 10,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 1,25</t>
+          <t>-17,17; 0,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 0,18</t>
+          <t>-23,18; -4,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 9,87</t>
+          <t>-5,8; 9,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -1,95</t>
+          <t>-14,76; -1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -5,12</t>
+          <t>-17,87; -4,71</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-34,51%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-39,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-1,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-31,11%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-53,82%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-34,51%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-39,17%</t>
+          <t>-53,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-46,6%</t>
+          <t>-46,79%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 49,26</t>
+          <t>-20,5; 80,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,94; 9,81</t>
+          <t>-58,94; 8,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,89; -16,88</t>
+          <t>-65,89; 4,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 83,01</t>
+          <t>-33,84; 52,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 6,4</t>
+          <t>-56,25; 4,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,23; 5,75</t>
+          <t>-74,79; -21,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 47,97</t>
+          <t>-19,9; 45,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,86; -7,62</t>
+          <t>-51,06; -6,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,57; -23,79</t>
+          <t>-63,57; -22,25</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,66</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,59</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,68</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-9,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-8,53</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,59</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-9,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,9</t>
+          <t>-6,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 8,59</t>
+          <t>-11,55; 9,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 1,81</t>
+          <t>-14,04; 6,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 2,32</t>
+          <t>-15,03; 11,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 9,69</t>
+          <t>-13,68; 9,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 5,51</t>
+          <t>-19,89; 1,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 10,87</t>
+          <t>-20,51; 2,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 5,06</t>
+          <t>-9,06; 5,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 0,25</t>
+          <t>-14,68; -0,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 3,53</t>
+          <t>-14,14; 2,07</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-2,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-11,29%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-14,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-41,17%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,76%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,32%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,98%</t>
+          <t>-40,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-20,79%</t>
+          <t>-25,49%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 53,92</t>
+          <t>-38,72; 52,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,61; 9,99</t>
+          <t>-50,75; 33,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,49; 15,26</t>
+          <t>-54,32; 61,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 50,79</t>
+          <t>-48,26; 50,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 28,59</t>
+          <t>-69,6; 15,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 57,33</t>
+          <t>-69,43; 19,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 25,43</t>
+          <t>-33,93; 25,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 2,38</t>
+          <t>-52,87; 0,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 18,3</t>
+          <t>-52,1; 11,14</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,56</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,85</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,07</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,86</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,7</t>
+          <t>-4,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,77</t>
+          <t>-5,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 14,44</t>
+          <t>-0,03; 13,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 4,68</t>
+          <t>-12,32; 0,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 5,39</t>
+          <t>-13,51; 0,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 13,77</t>
+          <t>0,91; 14,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 0,52</t>
+          <t>-7,25; 4,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 1,03</t>
+          <t>-10,59; 3,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,31</t>
+          <t>2,59; 12,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 0,87</t>
+          <t>-8,33; 0,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 1,12</t>
+          <t>-9,98; -0,72</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>31,58%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-26,16%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-29,3%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>36,49%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-5,85%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-18,46%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31,58%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-26,16%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-25,44%</t>
+          <t>-21,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-22,09%</t>
+          <t>-25,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 83,41</t>
+          <t>-1,65; 72,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 26,79</t>
+          <t>-47,41; 3,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 30,09</t>
+          <t>-52,09; 1,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 69,74</t>
+          <t>3,23; 81,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,27; 3,1</t>
+          <t>-30,63; 28,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 6,39</t>
+          <t>-44,86; 17,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,66; 61,62</t>
+          <t>10,0; 66,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 3,91</t>
+          <t>-33,89; 3,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 7,36</t>
+          <t>-41,93; -2,65</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,18</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,48</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,18</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,48</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,4</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,57</t>
+          <t>-2,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 13,4</t>
+          <t>1,35; 18,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 12,03</t>
+          <t>-10,55; 5,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 8,37</t>
+          <t>-13,17; 3,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 19,45</t>
+          <t>-2,46; 13,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 5,24</t>
+          <t>-4,06; 11,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 2,73</t>
+          <t>-7,21; 8,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 13,28</t>
+          <t>1,54; 13,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 5,61</t>
+          <t>-5,35; 6,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 2,8</t>
+          <t>-7,7; 3,4</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-12,2%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-24,57%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>37,22%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>25,94%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-12,2%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-26,53%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-14,29%</t>
+          <t>-13,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 126,4</t>
+          <t>5,83; 110,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,96; 116,92</t>
+          <t>-43,94; 34,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 74,1</t>
+          <t>-55,6; 18,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,83; 114,38</t>
+          <t>-12,36; 132,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 32,77</t>
+          <t>-23,25; 106,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 19,77</t>
+          <t>-38,8; 85,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,15; 85,96</t>
+          <t>6,98; 89,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 37,02</t>
+          <t>-25,17; 39,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 17,51</t>
+          <t>-38,54; 22,13</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5,56</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-4,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-9,42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-7,17</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-10,53</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-11,69</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-4,0</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-9,57</t>
+          <t>-11,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-10,66</t>
+          <t>-10,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 3,69</t>
+          <t>-5,87; 16,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 0,03</t>
+          <t>-13,9; 6,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,23; -2,13</t>
+          <t>-19,91; -0,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 16,39</t>
+          <t>-17,79; 4,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 5,51</t>
+          <t>-20,55; -0,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,94; -0,09</t>
+          <t>-20,7; -0,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 7,64</t>
+          <t>-8,08; 8,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -0,25</t>
+          <t>-13,47; 1,1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,39; -4,17</t>
+          <t>-16,98; -3,19</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-22,41%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-52,83%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-34,41%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-50,59%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-56,14%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-22,41%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-53,64%</t>
+          <t>-53,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-55,09%</t>
+          <t>-53,03%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-72,2; 24,19</t>
+          <t>-23,0; 128,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,58; 10,47</t>
+          <t>-61,74; 57,01</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,04; -2,86</t>
+          <t>-83,97; 3,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 132,37</t>
+          <t>-69,16; 30,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,4; 45,32</t>
+          <t>-76,94; 3,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,53; 5,65</t>
+          <t>-81,62; 6,37</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 48,05</t>
+          <t>-34,21; 56,98</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -1,04</t>
+          <t>-59,75; 6,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,59; -24,63</t>
+          <t>-74,57; -19,7</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5,55</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-4,88</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-6,85</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,53</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,17</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,32</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5,55</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-4,88</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-6,59</t>
+          <t>-4,61</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-5,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 7,21</t>
+          <t>1,59; 9,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 1,03</t>
+          <t>-8,28; -1,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -0,0</t>
+          <t>-10,51; -3,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,03</t>
+          <t>-0,27; 7,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -1,4</t>
+          <t>-5,38; 1,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -3,13</t>
+          <t>-8,21; -1,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,09</t>
+          <t>2,12; 7,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -1,15</t>
+          <t>-6,24; -1,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -2,92</t>
+          <t>-8,3; -3,1</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-22,23%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-31,17%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>17,7%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-10,89%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-21,67%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-22,23%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-29,98%</t>
+          <t>-23,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-26,19%</t>
+          <t>-27,49%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 38,83</t>
+          <t>6,72; 46,84</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 5,72</t>
+          <t>-34,69; -6,5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 1,43</t>
+          <t>-43,94; -15,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,89; 43,77</t>
+          <t>-1,44; 38,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-35,4; -6,87</t>
+          <t>-25,39; 7,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-43,57; -15,74</t>
+          <t>-37,78; -5,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,78; 36,18</t>
+          <t>9,29; 37,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-27,69; -6,03</t>
+          <t>-27,96; -7,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,03; -14,69</t>
+          <t>-37,06; -15,61</t>
         </is>
       </c>
     </row>
